--- a/data/trans_dic/P1418-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1418-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,31</t>
+          <t>2,77; 6,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,41</t>
+          <t>0,23; 2,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,59</t>
+          <t>0,83; 3,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,74</t>
+          <t>1,63; 4,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 11,11</t>
+          <t>5,33; 11,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,54</t>
+          <t>0,96; 4,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,61</t>
+          <t>2,21; 6,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,41</t>
+          <t>3,74; 7,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,61</t>
+          <t>4,21; 7,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,58</t>
+          <t>0,79; 2,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,27</t>
+          <t>1,77; 4,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,21</t>
+          <t>2,94; 5,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,8</t>
+          <t>2,91; 7,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,82</t>
+          <t>0,72; 3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,2; 1,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,84</t>
+          <t>1,46; 3,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,62</t>
+          <t>3,66; 8,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,68</t>
+          <t>2,97; 7,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,49</t>
+          <t>0,9; 4,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,05</t>
+          <t>3,77; 8,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,01</t>
+          <t>3,75; 6,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,76</t>
+          <t>1,96; 4,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,52</t>
+          <t>0,76; 2,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,22</t>
+          <t>2,91; 5,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,96</t>
+          <t>4,05; 8,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,09</t>
+          <t>1,94; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,49</t>
+          <t>1,0; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,26</t>
+          <t>3,25; 7,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 16,08</t>
+          <t>6,26; 16,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 16,39</t>
+          <t>7,4; 16,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,91</t>
+          <t>4,53; 13,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 19,65</t>
+          <t>11,33; 20,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,05</t>
+          <t>5,03; 8,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,43</t>
+          <t>4,14; 7,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,24</t>
+          <t>2,25; 5,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,49</t>
+          <t>6,02; 9,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,19 +1104,19 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>3,55%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,06</t>
+          <t>5,28; 8,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,15</t>
+          <t>3,38; 6,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,82</t>
+          <t>1,89; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,16</t>
+          <t>4,72; 7,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,1</t>
+          <t>6,22; 10,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,82</t>
+          <t>4,95; 8,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,37</t>
+          <t>3,37; 6,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,39</t>
+          <t>5,62; 8,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,31</t>
+          <t>6,04; 8,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,79</t>
+          <t>4,35; 6,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,5</t>
+          <t>2,76; 4,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,68</t>
+          <t>5,36; 7,29</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,35</t>
+          <t>4,63; 10,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,45</t>
+          <t>2,08; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,59</t>
+          <t>3,21; 6,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,13</t>
+          <t>3,17; 6,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 14,27</t>
+          <t>8,89; 14,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,91</t>
+          <t>10,97; 16,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,12</t>
+          <t>7,59; 12,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,45</t>
+          <t>11,98; 15,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,71</t>
+          <t>7,96; 11,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,29</t>
+          <t>7,65; 11,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,96</t>
+          <t>6,05; 9,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,86</t>
+          <t>8,73; 11,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,81</t>
+          <t>0,28; 2,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,17</t>
+          <t>0,34; 2,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 8,19</t>
+          <t>0,22; 7,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 14,58</t>
+          <t>10,79; 14,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 14,85</t>
+          <t>10,82; 14,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,14</t>
+          <t>7,85; 11,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,49</t>
+          <t>7,54; 10,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,98</t>
+          <t>9,03; 12,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,31</t>
+          <t>8,87; 12,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,35</t>
+          <t>6,36; 9,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,83</t>
+          <t>6,0; 9,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,34</t>
+          <t>4,75; 6,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,74</t>
+          <t>2,61; 3,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,77</t>
+          <t>3,64; 4,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 11,21</t>
+          <t>9,14; 11,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 10,8</t>
+          <t>8,65; 10,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,08</t>
+          <t>6,24; 8,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 9,35</t>
+          <t>8,16; 9,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,55</t>
+          <t>7,17; 8,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,13</t>
+          <t>5,9; 7,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,41</t>
+          <t>4,3; 5,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,85</t>
+          <t>6,15; 7,14</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>41125</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13068; 29897</t>
+          <t>13139; 30777</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1983; 10534</t>
+          <t>1016; 9295</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3100; 15417</t>
+          <t>3568; 15821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8744; 23926</t>
+          <t>8952; 23872</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16050; 34067</t>
+          <t>16342; 36140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3297; 14267</t>
+          <t>3011; 13597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7046; 22932</t>
+          <t>7660; 23540</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16405; 33067</t>
+          <t>18219; 36325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32733; 59372</t>
+          <t>32887; 59068</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6060; 19391</t>
+          <t>5971; 20780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14356; 33141</t>
+          <t>13775; 34895</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27773; 49607</t>
+          <t>30551; 53611</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31315</t>
+          <t>35883</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11623; 28632</t>
+          <t>10696; 27030</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3065; 15982</t>
+          <t>3012; 15974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>761; 7433</t>
+          <t>763; 6721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5860; 17335</t>
+          <t>7049; 19100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13061; 32060</t>
+          <t>13626; 31655</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9514; 25966</t>
+          <t>10054; 26082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3154; 16701</t>
+          <t>3349; 15883</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14059; 30763</t>
+          <t>15908; 33779</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27049; 51825</t>
+          <t>27683; 50998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15162; 36032</t>
+          <t>14806; 37294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5130; 18892</t>
+          <t>5680; 20050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22813; 43512</t>
+          <t>26306; 47586</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>51384</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21310; 43163</t>
+          <t>21985; 44552</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12740; 32013</t>
+          <t>12222; 31915</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5137; 18215</t>
+          <t>5201; 18523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8252; 41801</t>
+          <t>15281; 33664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10703; 26978</t>
+          <t>10511; 27149</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20416; 42629</t>
+          <t>19249; 42007</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7741; 23106</t>
+          <t>7532; 22070</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18617; 32795</t>
+          <t>21250; 37861</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35253; 64299</t>
+          <t>35751; 63052</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36286; 66067</t>
+          <t>36783; 65734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14558; 36056</t>
+          <t>15502; 36023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20253; 70826</t>
+          <t>39616; 63264</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60117</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>58144</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>113224</t>
+          <t>124530</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66852; 99862</t>
+          <t>65345; 100695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39652; 71324</t>
+          <t>39143; 70271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21186; 43879</t>
+          <t>21721; 44928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47186; 74038</t>
+          <t>53418; 83271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42859; 72126</t>
+          <t>44462; 72241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38608; 67462</t>
+          <t>37846; 67485</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27592; 52633</t>
+          <t>27794; 52928</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25579; 72179</t>
+          <t>48204; 70632</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118013; 162213</t>
+          <t>118026; 162583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87103; 130685</t>
+          <t>83734; 126115</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55073; 88993</t>
+          <t>54501; 88120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79366; 134197</t>
+          <t>106571; 144999</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>108286</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>132765</t>
+          <t>137970</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16440; 36272</t>
+          <t>16239; 36086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10833; 27822</t>
+          <t>10632; 27129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20850; 40919</t>
+          <t>19894; 40703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16622; 33723</t>
+          <t>17945; 36374</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50285; 81162</t>
+          <t>50545; 80252</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83440; 120942</t>
+          <t>83388; 121843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55664; 89487</t>
+          <t>56016; 88692</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80791; 129322</t>
+          <t>99228; 127829</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72041; 107613</t>
+          <t>73208; 108895</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100215; 143458</t>
+          <t>97252; 139912</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83535; 121788</t>
+          <t>82230; 122452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105647; 155412</t>
+          <t>121598; 158497</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>75102</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>79518</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>816; 8373</t>
+          <t>823; 7361</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>911; 8452</t>
+          <t>912; 7606</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>522; 19694</t>
+          <t>518; 18481</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>133068; 182073</t>
+          <t>134781; 180705</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>119904; 164593</t>
+          <t>119923; 165755</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86976; 131366</t>
+          <t>84922; 129123</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56341; 79774</t>
+          <t>63560; 90168</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>138017; 185355</t>
+          <t>139691; 187481</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123538; 169308</t>
+          <t>122045; 169191</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84935; 127966</t>
+          <t>87023; 130578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59342; 88346</t>
+          <t>64857; 97460</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136247</t>
+          <t>146768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>297872</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>434119</t>
+          <t>470409</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>155524; 207429</t>
+          <t>155222; 204573</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>85112; 128000</t>
+          <t>89382; 130295</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65071; 100052</t>
+          <t>64858; 100074</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104012; 160661</t>
+          <t>125048; 169145</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>309573; 378713</t>
+          <t>308666; 382930</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>311537; 383041</t>
+          <t>306717; 381793</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>222210; 285348</t>
+          <t>220409; 285741</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>244637; 333610</t>
+          <t>296073; 352918</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>481590; 568657</t>
+          <t>476480; 567485</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>409709; 496885</t>
+          <t>411159; 492480</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>296503; 374403</t>
+          <t>297400; 372884</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>370192; 475688</t>
+          <t>434064; 504462</t>
         </is>
       </c>
     </row>
